--- a/docs/review/packs/chapter-3.9.xlsx
+++ b/docs/review/packs/chapter-3.9.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Use valgus stress radiography where the grade decides the treatment.</t>
+          <t>Read opening in full extension as implicating the posteromedial structures.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Expect a healed ligament to be functional at a greater length than the original.</t>
+          <t>Use valgus stress radiography where the grade decides the treatment.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Treat valgus laxity as the finding that is easy to measure and easy to over-read in isolation.</t>
+          <t>Expect a healed ligament to be functional at a greater length than the original.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation, because rotatory laxity implicates the corner.</t>
+          <t>Treat valgus laxity as the finding that is easy to measure and easy to over-read in isolation.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -2041,22 +2041,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3.9.2-P1</t>
+          <t>3.9.1-P5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3.9.2</t>
+          <t>3.9.1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Assess external rotation as well as valgus on the medial side.</t>
+          <t>Assess rotation, because rotatory laxity implicates the corner.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.9.2-P2</t>
+          <t>3.9.2-P1</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Expect a larger rotatory laxity where a cruciate is also injured.</t>
+          <t>Assess external rotation as well as valgus on the medial side.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.9.2-P3</t>
+          <t>3.9.2-P2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Treat the absence of a reproducible instrument as a reason to examine under anaesthetic.</t>
+          <t>Expect a larger rotatory laxity where a cruciate is also injured.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.9.2-P4</t>
+          <t>3.9.2-P3</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Consider the meniscal attachment, since the deep layer attaches to it.</t>
+          <t>Treat the absence of a reproducible instrument as a reason to examine under anaesthetic.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.9.2-P5</t>
+          <t>3.9.2-P4</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Treat rotational laxity as the finding that decides whether a medial injury is operative, and valgus laxity as the finding that is easier to obtain.</t>
+          <t>Consider the meniscal attachment, since the deep layer attaches to it.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.9.2-P6</t>
+          <t>3.9.2-P5</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Examine under anaesthetic, since no instrument substitutes.</t>
+          <t>Treat rotational laxity as the finding that decides whether a medial injury is operative, and valgus laxity as the finding that is easier to obtain.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2191,22 +2191,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.9.3-P1</t>
+          <t>3.9.2-P6</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.9.3</t>
+          <t>3.9.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Localise the injury proximally or distally, since healing differs.</t>
+          <t>Decide the operative question on rotational rather than coronal laxity.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2216,22 +2216,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.9.3-P2</t>
+          <t>3.9.2-P7</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.9.3</t>
+          <t>3.9.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Expect healing with residual length rather than restored length.</t>
+          <t>Examine under anaesthetic, since no instrument substitutes.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2241,22 +2241,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.9.3-P3</t>
+          <t>3.9.2-P8</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.9.3</t>
+          <t>3.9.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Place a reconstruction's femoral attachment proximal and posterior to the epicondyle.</t>
+          <t>Correct alignment where it would load the reconstruction.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.9.3-P4</t>
+          <t>3.9.3-P1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Treat this ligament's healing capacity as the governing fact of medial side management and as the reason the operative subgroup is narrow.</t>
+          <t>Localise the injury proximally or distally, since healing differs.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.9.3-P5</t>
+          <t>3.9.3-P2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Place the femoral attachment anatomically, since position sets the length change pattern.</t>
+          <t>Expect healing with residual length rather than restored length.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,12 +2316,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.9.4-P1</t>
+          <t>3.9.3-P3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.9.4</t>
+          <t>3.9.3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Expect isolated injury here to present as rotatory rather than coronal laxity.</t>
+          <t>Place a reconstruction's femoral attachment proximal and posterior to the epicondyle.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,22 +2341,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.9.4-P2</t>
+          <t>3.9.3-P4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3.9.4</t>
+          <t>3.9.3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Assess the layer and the meniscus together rather than separately.</t>
+          <t>Treat this ligament's healing capacity as the governing fact of medial side management and as the reason the operative subgroup is narrow.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,12 +2366,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.9.4-P3</t>
+          <t>3.9.3-P5</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.9.4</t>
+          <t>3.9.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Treat the meniscotibial attachment as the structure that links medial ligament injury to meniscal extrusion, and treat extrusion as the imaging sign that it has failed.</t>
+          <t>Reserve operative treatment for displacement, failed healing or rotatory laxity.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,12 +2391,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.9.4-P4</t>
+          <t>3.9.3-P6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.9.4</t>
+          <t>3.9.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Measure meniscal extrusion in a medial ligament injury.</t>
+          <t>Place the femoral attachment anatomically, since position sets the length change pattern.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,12 +2416,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.9.4-P5</t>
+          <t>3.9.3-P7</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.9.4</t>
+          <t>3.9.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Repair the meniscotibial attachment where it is disrupted and repairable.</t>
+          <t>Correct a valgus limb that is loading the medial side.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.9.4-P6</t>
+          <t>3.9.4-P1</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Treat the meniscal consequence as the one with the degenerative endpoint.</t>
+          <t>Expect isolated injury here to present as rotatory rather than coronal laxity.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,12 +2466,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.9.5-P1</t>
+          <t>3.9.4-P2</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.9.5</t>
+          <t>3.9.4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Expect apportionment figures here to be less precise than for a discrete ligament.</t>
+          <t>Assess the layer and the meniscus together rather than separately.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,12 +2491,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.9.5-P2</t>
+          <t>3.9.4-P3</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.9.5</t>
+          <t>3.9.4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Consider semimembranosus function as part of the dynamic restraint.</t>
+          <t>Accept that no clinical test isolates this layer.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,12 +2516,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.9.5-P3</t>
+          <t>3.9.4-P4</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.9.5</t>
+          <t>3.9.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Treat the posterior oblique ligament as the structure whose involvement converts a medial injury from non operative to operative, and treat the examination in extension as the way that is established.</t>
+          <t>Treat the meniscotibial attachment as the structure that links medial ligament injury to meniscal extrusion, and treat extrusion as the imaging sign that it has failed.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,12 +2541,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.9.5-P4</t>
+          <t>3.9.4-P5</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.9.5</t>
+          <t>3.9.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Address it in a chronic reconstruction even where the acute injury spared it.</t>
+          <t>Measure meniscal extrusion in a medial ligament injury.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,12 +2566,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.9.5-P5</t>
+          <t>3.9.4-P6</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.9.5</t>
+          <t>3.9.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography in extension as well as at 30 degrees.</t>
+          <t>Repair the meniscotibial attachment where it is disrupted and repairable.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,22 +2591,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.9.6-P1</t>
+          <t>3.9.4-P7</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.9.6</t>
+          <t>3.9.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Examine in full extension to detect corner involvement.</t>
+          <t>Treat the meniscal consequence as the one with the degenerative endpoint.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,12 +2616,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.9.6-P2</t>
+          <t>3.9.5-P1</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.9.6</t>
+          <t>3.9.5</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Expect a combined superficial and corner injury to be considerably more lax than either alone.</t>
+          <t>Read opening in extension as implicating the posteromedial structures.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.9.6-P3</t>
+          <t>3.9.5-P2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.9.6</t>
+          <t>3.9.5</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Treat the corner as a unit clinically, since no test separates its members.</t>
+          <t>Expect apportionment figures here to be less precise than for a discrete ligament.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,22 +2666,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.9.6-P4</t>
+          <t>3.9.5-P3</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.9.6</t>
+          <t>3.9.5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Treat the corner as the structure that decides the medial side's management.</t>
+          <t>Consider semimembranosus function as part of the dynamic restraint.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,22 +2691,22 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.9.7-P1</t>
+          <t>3.9.5-P4</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.9.7</t>
+          <t>3.9.5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Use the dial test at 30 and 90 degrees to separate medial from lateral rotatory involvement.</t>
+          <t>Treat the posterior oblique ligament as the structure whose involvement converts a medial injury from non operative to operative, and treat the examination in extension as the way that is established.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,22 +2716,22 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.9.7-P2</t>
+          <t>3.9.5-P5</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.9.7</t>
+          <t>3.9.5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Expect the pattern to be clearest under anaesthetic.</t>
+          <t>Address it in a chronic reconstruction even where the acute injury spared it.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,22 +2741,22 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.9.7-P3</t>
+          <t>3.9.5-P6</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.9.7</t>
+          <t>3.9.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Treat the pattern as implying corner involvement.</t>
+          <t>Measure the result with stress radiography in extension as well as at 30 degrees.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,22 +2766,22 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.9.7-P4</t>
+          <t>3.9.6-P1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.9.7</t>
+          <t>3.9.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat this pattern as the reason a medial injury alongside a cruciate tear sometimes needs surgery.</t>
+          <t>Examine in full extension to detect corner involvement.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,22 +2791,22 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.9.7-P5</t>
+          <t>3.9.6-P2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.9.7</t>
+          <t>3.9.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Assess anteromedial rotation under anaesthetic after cruciate fixation.</t>
+          <t>Expect a combined superficial and corner injury to be considerably more lax than either alone.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,22 +2816,22 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.9.7-P6</t>
+          <t>3.9.6-P3</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.9.7</t>
+          <t>3.9.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Address the medial side at the same sitting where rotatory laxity persists.</t>
+          <t>Treat the corner as a unit clinically, since no test separates its members.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,12 +2841,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.9.8-P1</t>
+          <t>3.9.6-P4</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.9.8</t>
+          <t>3.9.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Repair rather than reconstruction is possible acutely, particularly for a displaced distal avulsion.</t>
+          <t>Read apportionment figures within the corner as less settled than those between corner and superficial ligament.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.9.8-P2</t>
+          <t>3.9.6-P5</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.9.8</t>
+          <t>3.9.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Place both limbs anatomically, since position sets the pattern.</t>
+          <t>Treat the corner as the structure that decides the medial side's management.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,12 +2891,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.9.8-P3</t>
+          <t>3.9.7-P1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.9.8</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Check flexion after fixation, since over-constraint presents that way.</t>
+          <t>Use the dial test at 30 and 90 degrees to separate medial from lateral rotatory involvement.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,12 +2916,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.9.8-P4</t>
+          <t>3.9.7-P2</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.9.8</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Consider acute repair where a displaced distal avulsion is present.</t>
+          <t>Expect the pattern to be clearest under anaesthetic.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,22 +2941,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.9.8-P5</t>
+          <t>3.9.7-P3</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.9.8</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Treat the indication as the harder question than the technique.</t>
+          <t>Treat the pattern as implying corner involvement.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,22 +2966,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.9.8-P6</t>
+          <t>3.9.7-P4</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.9.8</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Localise the deformity to the femur or the tibia before planning.</t>
+          <t>Treat this pattern as the reason a medial injury alongside a cruciate tear sometimes needs surgery.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,22 +2991,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.9.9-P1</t>
+          <t>3.9.7-P5</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.9.9</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Order dependence is the standing limitation, and it is larger where structures are adjacent capsular layers.</t>
+          <t>Assess anteromedial rotation under anaesthetic after cruciate fixation.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,22 +3016,22 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.9.9-P2</t>
+          <t>3.9.7-P6</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.9.9</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Examine at full extension and at 20 to 30 degrees deliberately, as a sampling strategy.</t>
+          <t>Address the medial side at the same sitting where rotatory laxity persists.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,22 +3041,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.9.9-P3</t>
+          <t>3.9.7-P7</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.9.9</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Expect order dependence to be worse where the structures are adjacent capsular layers.</t>
+          <t>Correct valgus alignment where it loads the medial reconstruction.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.9.9-P4</t>
+          <t>3.9.7-P8</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.9.9</t>
+          <t>3.9.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Treat the angle dependence as the thing that makes a medial reconstruction a two limb operation and the thing that makes tensioning angles matter.</t>
+          <t>Accept that the rotatory component cannot be quantified clinically.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.9.9-P5</t>
+          <t>3.9.8-P1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.9.9</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Measure the postoperative result at both angles, not one.</t>
+          <t>Repair rather than reconstruction is possible acutely, particularly for a displaced distal avulsion.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,22 +3116,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.9.9-P6</t>
+          <t>3.9.8-P2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.9.9</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Expect a single limb construct to leave one angle less controlled.</t>
+          <t>Place both limbs anatomically, since position sets the pattern.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,12 +3141,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P1</t>
+          <t>3.9.8-P3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.9.10</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Address the medial side where laxity persists, since it loads the graft.</t>
+          <t>Check flexion after fixation, since over-constraint presents that way.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,22 +3166,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P2</t>
+          <t>3.9.8-P4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.9.10</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Treat the sequencing as the decision and the mechanics as what informs it.</t>
+          <t>Consider acute repair where a displaced distal avulsion is present.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,12 +3191,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P3</t>
+          <t>3.9.8-P5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.9.10</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Restore motion before reconstructing the cruciate.</t>
+          <t>Treat the indication as the harder question than the technique.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P4</t>
+          <t>3.9.8-P6</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.9.10</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Address the medial side at that sitting only if laxity persists.</t>
+          <t>Reserve the operation for failed healing, rotatory laxity or a displaced avulsion.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,12 +3241,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P5</t>
+          <t>3.9.8-P7</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.9.10</t>
+          <t>3.9.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3256,16 +3256,416 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Repair acutely where there is a displaced medial avulsion or gross instability.</t>
+          <t>Correct valgus alignment where it would load the reconstruction.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3.9.8-P8</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>3.9.8</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Correct a valgus deformity before or with a medial reconstruction.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>3.9.8-P9</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>3.9.8</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Localise the deformity to the femur or the tibia before planning.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P1</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Order dependence is the standing limitation, and it is larger where structures are adjacent capsular layers.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P2</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Examine at full extension and at 20 to 30 degrees deliberately, as a sampling strategy.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P3</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Read differences between published figures as protocol differences.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P4</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Expect order dependence to be worse where the structures are adjacent capsular layers.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P5</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Treat the angle dependence as the thing that makes a medial reconstruction a two limb operation and the thing that makes tensioning angles matter.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P6</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Measure the postoperative result at both angles, not one.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P7</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Expect a single limb construct to leave one angle less controlled.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9-P8</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3.9.9</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Accept that a residual laxity cannot be attributed to a specific limb.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P1</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Address the medial side where laxity persists, since it loads the graft.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P2</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Weigh the stiffness risk of early combined surgery against the laxity risk of delay.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P3</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Treat the sequencing as the decision and the mechanics as what informs it.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P4</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Restore motion before reconstructing the cruciate.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P5</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Address the medial side at that sitting only if laxity persists.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P6</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Repair acutely where there is a displaced medial avulsion or gross instability.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3746,7 +4146,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>53</f>
+        <f>69</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3761,7 +4161,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3791,7 +4191,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3803,7 +4203,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3815,7 +4215,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -3827,7 +4227,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.9.xlsx
+++ b/docs/review/packs/chapter-3.9.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Read differences between published figures as protocol differences.</t>
+          <t>Record the angle with any laxity finding.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Expect order dependence to be worse where the structures are adjacent capsular layers.</t>
+          <t>Read differences between published figures as protocol differences.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Treat the angle dependence as the thing that makes a medial reconstruction a two limb operation and the thing that makes tensioning angles matter.</t>
+          <t>Expect order dependence to be worse where the structures are adjacent capsular layers.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Measure the postoperative result at both angles, not one.</t>
+          <t>Treat the angle dependence as the thing that makes a medial reconstruction a two limb operation and the thing that makes tensioning angles matter.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Expect a single limb construct to leave one angle less controlled.</t>
+          <t>Measure the postoperative result at both angles, not one.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Accept that a residual laxity cannot be attributed to a specific limb.</t>
+          <t>Expect a single limb construct to leave one angle less controlled.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3516,22 +3516,22 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P1</t>
+          <t>3.9.9-P9</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>3.9.10</t>
+          <t>3.9.9</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Address the medial side where laxity persists, since it loads the graft.</t>
+          <t>Accept that a residual laxity cannot be attributed to a specific limb.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3541,7 +3541,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P2</t>
+          <t>3.9.10-P1</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Weigh the stiffness risk of early combined surgery against the laxity risk of delay.</t>
+          <t>Address the medial side where laxity persists, since it loads the graft.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P3</t>
+          <t>3.9.10-P2</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Treat the sequencing as the decision and the mechanics as what informs it.</t>
+          <t>Weigh the stiffness risk of early combined surgery against the laxity risk of delay.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3591,7 +3591,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P4</t>
+          <t>3.9.10-P3</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Restore motion before reconstructing the cruciate.</t>
+          <t>Treat the sequencing as the decision and the mechanics as what informs it.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P5</t>
+          <t>3.9.10-P4</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Address the medial side at that sitting only if laxity persists.</t>
+          <t>Restore motion before reconstructing the cruciate.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.9.10-P6</t>
+          <t>3.9.10-P5</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3656,16 +3656,41 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Repair acutely where there is a displaced medial avulsion or gross instability.</t>
+          <t>Address the medial side at that sitting only if laxity persists.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10-P6</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.9.10</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Repair acutely where there is a displaced medial avulsion or gross instability.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4146,7 +4171,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>69</f>
+        <f>70</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -4161,7 +4186,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -4191,7 +4216,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -4203,7 +4228,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -4215,7 +4240,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -4227,7 +4252,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
